--- a/branches/review/2027.0.0-ballot2-en/ValueSet-mii-vs-mikrobio-voraussichtliche-empfindlichkeit.xlsx
+++ b/branches/review/2027.0.0-ballot2-en/ValueSet-mii-vs-mikrobio-voraussichtliche-empfindlichkeit.xlsx
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Result ValueSet for predicted susceptibility: the expected category susceptible, intermediate or resistant derived from genotypic detections.</t>
+    <t>Result ValueSet for predicted susceptibility: the predicted category susceptible, intermediate or resistant derived from genotypic detections.</t>
   </si>
   <si>
     <t>Purpose</t>
